--- a/data/Неделя_06.07-12.07_2026.xlsx
+++ b/data/Неделя_06.07-12.07_2026.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s.kulikova\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s.kulikova\Desktop\ИИ\Аналитика данных по качеству\Месяц АН\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{213B71FC-C7E7-42AF-BA4C-E8F9935BEBA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81A7FB52-E91C-4A12-B8A5-915026D74407}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="22320" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="104">
   <si>
     <t>№ п/п</t>
   </si>
@@ -86,9 +86,6 @@
   </si>
   <si>
     <t>(ПФК) Секция заполнения СЗ-3000 (сварка)</t>
-  </si>
-  <si>
-    <t>УУ Перильные ограждения</t>
   </si>
   <si>
     <t>Дефекты сварных швов</t>
@@ -125,9 +122,6 @@
     <t>(ПФК) Основание (М 009.80.01.000 СБ) (сварка)</t>
   </si>
   <si>
-    <t>УУ Мачты</t>
-  </si>
-  <si>
     <t>Невыполнение требований НТД</t>
   </si>
   <si>
@@ -170,9 +164,6 @@
     <t>(ПФК) Перильное ограждение П2 (Ц 208.03.00.000 СБ) (снятие фасок)</t>
   </si>
   <si>
-    <t>УУ Металлоконструкции</t>
-  </si>
-  <si>
     <t>1. Сварной шов неполной длины. 2. Брызги металла. 3.  Плохое повторное возбуждение дуги. 4. Кратеры. 5. Натеки. 6. Цепочка застывших капель. 7. Отсутствие штампа самоконтроля.</t>
   </si>
   <si>
@@ -200,9 +191,6 @@
     <t>К00-0000242</t>
   </si>
   <si>
-    <t>ДиМ</t>
-  </si>
-  <si>
     <t>Отсутствует печать самоконтроля</t>
   </si>
   <si>
@@ -215,9 +203,6 @@
     <t>(ПФК) Закладная деталь стойки перильного ограждения ЗДСПО (сварка)</t>
   </si>
   <si>
-    <t>Пешеходные ограждения (детали) по СТО 036</t>
-  </si>
-  <si>
     <t>Плохое повторное возбуждение дуги, кратеры</t>
   </si>
   <si>
@@ -233,9 +218,6 @@
     <t>ГПЦ(настил)(40) Настил SP 34х38/30х3 S5 А Zn 1280х1000 (РН 177.00.00.000-08)</t>
   </si>
   <si>
-    <t>Настилы СТО 049</t>
-  </si>
-  <si>
     <t>Бурая ржавчина</t>
   </si>
   <si>
@@ -245,9 +227,6 @@
     <t>ГПЦ(настил)(40) Настил SP 34х38/30х3 S5 А Zn 1280х1167</t>
   </si>
   <si>
-    <t>Опоры по СТО 350</t>
-  </si>
-  <si>
     <t>К00-0000245</t>
   </si>
   <si>
@@ -266,9 +245,6 @@
     <t>(ПФК) Рама Э 357.01.01.000 (сварка)</t>
   </si>
   <si>
-    <t>1.01.15 Воротная система (серийное производство)</t>
-  </si>
-  <si>
     <t>1. Брызги металла. 2. Поры. 3. Подрезы.</t>
   </si>
   <si>
@@ -281,9 +257,6 @@
     <t>ГПЦ(60) Консоль-амортизатор КА (БО 248.01.00.002-01)</t>
   </si>
   <si>
-    <t>УУ Дорожные ограждения (внутренний рынок)</t>
-  </si>
-  <si>
     <t>Не соответствует марка стали и /или материал</t>
   </si>
   <si>
@@ -339,6 +312,27 @@
   </si>
   <si>
     <t>Невозможно установить</t>
+  </si>
+  <si>
+    <t>ПО</t>
+  </si>
+  <si>
+    <t>Мачты</t>
+  </si>
+  <si>
+    <t>МК, другое</t>
+  </si>
+  <si>
+    <t>Настилы сварные</t>
+  </si>
+  <si>
+    <t>ОО</t>
+  </si>
+  <si>
+    <t>ВО</t>
+  </si>
+  <si>
+    <t>ДО</t>
   </si>
 </sst>
 </file>
@@ -837,7 +831,7 @@
         <v>21</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>22</v>
+        <v>97</v>
       </c>
       <c r="G2" s="3">
         <v>44</v>
@@ -846,34 +840,34 @@
         <v>783.2</v>
       </c>
       <c r="I2" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="K2" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="L2" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="M2" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="N2" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="O2" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="P2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q2" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="P2" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q2" s="5" t="s">
+      <c r="R2" s="5" t="s">
         <v>30</v>
-      </c>
-      <c r="R2" s="5" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="22.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -881,7 +875,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>19</v>
@@ -890,10 +884,10 @@
         <v>20</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
       <c r="G3" s="3">
         <v>4</v>
@@ -902,34 +896,34 @@
         <v>46.12</v>
       </c>
       <c r="I3" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="K3" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="L3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="N3" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="O3" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="L3" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="N3" s="5" t="s">
+      <c r="P3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q3" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="O3" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="P3" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q3" s="5" t="s">
-        <v>40</v>
-      </c>
       <c r="R3" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
@@ -937,10 +931,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>20</v>
@@ -949,7 +943,7 @@
         <v>21</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>22</v>
+        <v>97</v>
       </c>
       <c r="G4" s="3">
         <v>44</v>
@@ -958,34 +952,34 @@
         <v>783.2</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K4" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="L4" s="5" t="s">
+      <c r="M4" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="M4" s="5" t="s">
+      <c r="N4" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="N4" s="5" t="s">
+      <c r="O4" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="O4" s="5" t="s">
+      <c r="P4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q4" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="P4" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q4" s="5" t="s">
+      <c r="R4" s="5" t="s">
         <v>30</v>
-      </c>
-      <c r="R4" s="5" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
@@ -993,19 +987,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>22</v>
+        <v>97</v>
       </c>
       <c r="G5" s="3">
         <v>19</v>
@@ -1014,16 +1008,16 @@
         <v>247.76</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K5" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" s="5" t="s">
         <v>25</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>26</v>
       </c>
       <c r="M5" s="5"/>
       <c r="N5" s="5"/>
@@ -1037,19 +1031,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>49</v>
+        <v>99</v>
       </c>
       <c r="G6" s="3">
         <v>14</v>
@@ -1058,16 +1052,16 @@
         <v>1119.44</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="K6" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6" s="5" t="s">
         <v>25</v>
-      </c>
-      <c r="L6" s="5" t="s">
-        <v>26</v>
       </c>
       <c r="M6" s="5"/>
       <c r="N6" s="5"/>
@@ -1075,7 +1069,7 @@
       <c r="P6" s="5"/>
       <c r="Q6" s="5"/>
       <c r="R6" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
@@ -1083,19 +1077,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
       <c r="G7" s="3">
         <v>1</v>
@@ -1104,16 +1098,16 @@
         <v>1570.55</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="K7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" s="5" t="s">
         <v>25</v>
-      </c>
-      <c r="L7" s="5" t="s">
-        <v>26</v>
       </c>
       <c r="M7" s="5"/>
       <c r="N7" s="5"/>
@@ -1121,7 +1115,7 @@
       <c r="P7" s="5"/>
       <c r="Q7" s="5"/>
       <c r="R7" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="10.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -1129,19 +1123,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>22</v>
+        <v>97</v>
       </c>
       <c r="G8" s="3">
         <v>45</v>
@@ -1150,16 +1144,16 @@
         <v>519.75</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="K8" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="5" t="s">
         <v>25</v>
-      </c>
-      <c r="L8" s="5" t="s">
-        <v>26</v>
       </c>
       <c r="M8" s="5"/>
       <c r="N8" s="5"/>
@@ -1173,19 +1167,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="G9" s="3">
         <v>30</v>
@@ -1194,22 +1188,22 @@
         <v>2398.8000000000002</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L9" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M9" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="M9" s="5" t="s">
-        <v>27</v>
-      </c>
       <c r="N9" s="5" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="O9" s="5"/>
       <c r="P9" s="5"/>
@@ -1221,19 +1215,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>64</v>
+        <v>97</v>
       </c>
       <c r="G10" s="3">
         <v>35</v>
@@ -1242,22 +1236,22 @@
         <v>232.05</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L10" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M10" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="M10" s="5" t="s">
-        <v>27</v>
-      </c>
       <c r="N10" s="5" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="O10" s="5"/>
       <c r="P10" s="5"/>
@@ -1269,19 +1263,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>21</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>64</v>
+        <v>97</v>
       </c>
       <c r="G11" s="3">
         <v>40</v>
@@ -1290,22 +1284,22 @@
         <v>712</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L11" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M11" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="M11" s="5" t="s">
-        <v>27</v>
-      </c>
       <c r="N11" s="5" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="O11" s="5"/>
       <c r="P11" s="5"/>
@@ -1317,19 +1311,19 @@
         <v>12</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="G12" s="3">
         <v>1</v>
@@ -1338,22 +1332,22 @@
         <v>34.78</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L12" s="5" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="M12" s="5" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="N12" s="5" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="O12" s="5"/>
       <c r="P12" s="5"/>
@@ -1365,19 +1359,19 @@
         <v>13</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="G13" s="3">
         <v>1</v>
@@ -1386,22 +1380,22 @@
         <v>17.059999999999999</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="M13" s="5" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="N13" s="5" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="O13" s="5"/>
       <c r="P13" s="5"/>
@@ -1413,19 +1407,19 @@
         <v>14</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D14" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E14" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E14" s="5" t="s">
-        <v>73</v>
-      </c>
       <c r="F14" s="5" t="s">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="G14" s="3">
         <v>1</v>
@@ -1434,22 +1428,22 @@
         <v>39.619999999999997</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L14" s="5" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="M14" s="5" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="N14" s="5" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="O14" s="5"/>
       <c r="P14" s="5"/>
@@ -1461,19 +1455,19 @@
         <v>17</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>74</v>
+        <v>101</v>
       </c>
       <c r="G15" s="3">
         <v>2</v>
@@ -1482,22 +1476,22 @@
         <v>2442.1799999999998</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L15" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M15" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="M15" s="5" t="s">
-        <v>27</v>
-      </c>
       <c r="N15" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="O15" s="5"/>
       <c r="P15" s="5"/>
@@ -1509,19 +1503,19 @@
         <v>26</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="G16" s="3">
         <v>1</v>
@@ -1530,22 +1524,22 @@
         <v>189.6</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="L16" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M16" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="M16" s="5" t="s">
+      <c r="N16" s="5" t="s">
         <v>27</v>
-      </c>
-      <c r="N16" s="5" t="s">
-        <v>28</v>
       </c>
       <c r="O16" s="5"/>
       <c r="P16" s="5"/>
@@ -1557,19 +1551,19 @@
         <v>28</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="G17" s="3">
         <v>600</v>
@@ -1578,14 +1572,14 @@
         <v>1977.6</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="J17" s="5"/>
       <c r="K17" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L17" s="5" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="M17" s="5"/>
       <c r="N17" s="5"/>
@@ -1599,19 +1593,19 @@
         <v>29</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>22</v>
+        <v>97</v>
       </c>
       <c r="G18" s="3">
         <v>1</v>
@@ -1620,16 +1614,16 @@
         <v>44.9</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L18" s="5" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="M18" s="5"/>
       <c r="N18" s="5"/>
@@ -1643,19 +1637,19 @@
         <v>30</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="G19" s="3">
         <v>1</v>
@@ -1664,16 +1658,16 @@
         <v>54.3</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L19" s="5" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="M19" s="5"/>
       <c r="N19" s="5"/>
@@ -1687,19 +1681,19 @@
         <v>31</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="G20" s="3">
         <v>25</v>
@@ -1708,14 +1702,14 @@
         <v>25.75</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="J20" s="5"/>
       <c r="K20" s="5" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="L20" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M20" s="5"/>
       <c r="N20" s="5"/>
